--- a/2nd lab/ЛР2_Михальчук_Антон_Excel.xlsx
+++ b/2nd lab/ЛР2_Михальчук_Антон_Excel.xlsx
@@ -1,43 +1,280 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B4A75B4-CBD2-47A4-ADF4-AD025B39E01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Дані" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sensitivity Report" sheetId="3" r:id="rId1"/>
+    <sheet name="Answer Report" sheetId="2" r:id="rId2"/>
+    <sheet name="Дані" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">Дані!$B$11:$E$11</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">Дані!$G$4:$G$8</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">Дані!$B$13</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">Дані!$F$4:$F$8</definedName>
+    <definedName name="solver_rxc1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rxv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+  <si>
+    <t>Microsoft Excel Sensitivity Report</t>
+  </si>
+  <si>
+    <t>Worksheet: Answer Report</t>
+  </si>
+  <si>
+    <t>Report Created:Sun Oct 04 2026 13:13:31 GMT+0300 (Eastern European Summer Time)</t>
+  </si>
+  <si>
+    <t>Engine: LP/Quadratic</t>
+  </si>
+  <si>
+    <t>Objective Cell (Max)</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Original Value</t>
+  </si>
+  <si>
+    <t>Final Value</t>
+  </si>
+  <si>
+    <t>Дані'!B13</t>
+  </si>
+  <si>
+    <t>Decision Variable Cells</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Reduced</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Objective Coefficient</t>
+  </si>
+  <si>
+    <t>$B$11</t>
+  </si>
+  <si>
+    <t>$C$11</t>
+  </si>
+  <si>
+    <t>$D$11</t>
+  </si>
+  <si>
+    <t>$E$11</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Shadow</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Allowable</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>R.H.Side</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Decrease</t>
+  </si>
+  <si>
+    <t>$G$4</t>
+  </si>
+  <si>
+    <t>$G$5</t>
+  </si>
+  <si>
+    <t>$G$6</t>
+  </si>
+  <si>
+    <t>$G$7</t>
+  </si>
+  <si>
+    <t>$G$8</t>
+  </si>
+  <si>
+    <t>Microsoft Excel Answer Report</t>
+  </si>
+  <si>
+    <t>Worksheet: Дані</t>
+  </si>
+  <si>
+    <t>Report Created:Sun Oct 04 2026 13:13:30 GMT+0300 (Eastern European Summer Time)</t>
+  </si>
+  <si>
+    <t>Result: Solver found a solution.  All constraints and optimality conditions are satisfied.</t>
+  </si>
+  <si>
+    <t>Solution Time: 2 milliseconds</t>
+  </si>
+  <si>
+    <t>Iterations: 0</t>
+  </si>
+  <si>
+    <t>Subproblems: 0</t>
+  </si>
+  <si>
+    <t>Incumbent Solutions: 0</t>
+  </si>
+  <si>
+    <t>Lower Bound</t>
+  </si>
+  <si>
+    <t>Upper Bound</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Варіант 13 · «Астро-ТВ» · телевізори, шт./день</t>
+  </si>
+  <si>
+    <t>Ресурс</t>
+  </si>
+  <si>
+    <t>Astro</t>
+  </si>
+  <si>
+    <t>Cosmo</t>
+  </si>
+  <si>
+    <t>Nova</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>Запас</t>
+  </si>
+  <si>
+    <t>Конвеєр A, год</t>
+  </si>
+  <si>
+    <t>Конвеєр Б, год</t>
+  </si>
+  <si>
+    <t>Цех кінескопів, год</t>
+  </si>
+  <si>
+    <t>Цех корпусів, год</t>
+  </si>
+  <si>
+    <t>Ділянка збирання, год</t>
+  </si>
+  <si>
+    <t>Прибуток з одиниці</t>
+  </si>
+  <si>
+    <t>План</t>
+  </si>
+  <si>
+    <t>Прибуток</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Helv"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Helv"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helv"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,86 +282,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -411,184 +613,861 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{95E8764C-F408-4C7C-AFE2-BD5B56219B54}">
+  <we:reference id="wa104100404" version="3.0.0.1" store="en-US" storeType="omex"/>
+  <we:alternateReferences>
+    <we:reference id="wa104100404" version="3.0.0.1" store="en-US" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="UniqueID" value="&quot;2026941791108319307&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{503B3E66-A62B-4B42-82B0-377A0D919892}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Варіант 13 · «Астро-ТВ» · телевізори, шт./день</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Ресурс</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Astro</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Cosmo</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Nova</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Vega</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Запас</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Конвеєр A, год</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="n">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10269.833333333334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3">
+        <v>69.833333333333343</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>76.000000099999994</v>
+      </c>
+      <c r="F13" s="3">
+        <v>52.999999899999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-11.333333333333329</v>
+      </c>
+      <c r="E14" s="3">
+        <v>53.333333333333329</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1E+30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-6</v>
+      </c>
+      <c r="E15" s="3">
+        <v>59</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-1E+30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5">
+        <v>323.66666666666669</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>27.500000074999996</v>
+      </c>
+      <c r="F16" s="5">
+        <v>14.749999975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="3">
+        <v>69.833333333333343</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>937</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1E+30</v>
+      </c>
+      <c r="G21" s="3">
+        <v>867.16666666666674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1390</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1390</v>
+      </c>
+      <c r="F22" s="3">
+        <v>74.5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>485.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="3">
+        <v>603</v>
+      </c>
+      <c r="D23" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>603</v>
+      </c>
+      <c r="F23" s="3">
+        <v>323.66666666666663</v>
+      </c>
+      <c r="G23" s="3">
+        <v>49.666666666666629</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="3">
+        <v>971</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1120</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1E+30</v>
+      </c>
+      <c r="G24" s="3">
+        <v>148.99999999999989</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1180.5</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1334</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1E+30</v>
+      </c>
+      <c r="G25" s="5">
+        <v>153.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC1E64F-81D1-4367-9CC1-E23F353EB8BA}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>10269.833333333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>69.833333333333343</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>323.66666666666669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>69.833333333333343</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1E+30</v>
+      </c>
+      <c r="F26" s="3">
         <v>937</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Конвеєр Б, год</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="G26" s="3">
+        <v>867.16666666666663</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1390</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1E+30</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1390</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3">
+        <v>603</v>
+      </c>
+      <c r="E28" s="3">
+        <v>-1E+30</v>
+      </c>
+      <c r="F28" s="3">
+        <v>603</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>971</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-1E+30</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1120</v>
+      </c>
+      <c r="G29" s="3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1180.5</v>
+      </c>
+      <c r="E30" s="5">
+        <v>-1E+30</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1334</v>
+      </c>
+      <c r="G30" s="5">
+        <v>153.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>937</v>
+      </c>
+      <c r="G4">
+        <f>SUMPRODUCT(B4:E4, $B$11:$E$11)</f>
+        <v>69.833333333333343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>1390</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Цех кінескопів, год</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="G5">
+        <f t="shared" ref="G5:G8" si="0">SUMPRODUCT(B5:E5, $B$11:$E$11)</f>
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>603</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Цех корпусів, год</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1120</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Ділянка збирання, год</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>971</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>1334</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Прибуток з одиниці</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>1180.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9">
         <v>59</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>53</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11">
+        <v>69.833333333333343</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>323.66666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13">
+        <f>SUMPRODUCT(B9:E9, B11:E11)</f>
+        <v>10269.833333333334</v>
       </c>
     </row>
   </sheetData>
